--- a/data/trans_orig/P29A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P29A-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2007</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2007 (tasa de respuesta: 99,08%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>120286</t>
+          <t>121382</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154506</t>
+          <t>153586</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>45,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,47%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60437</t>
+          <t>57539</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>89498</t>
+          <t>86926</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>191022</t>
+          <t>187223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>235404</t>
+          <t>232070</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,53%</t>
+          <t>43,9%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>114337</t>
+          <t>115257</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>148557</t>
+          <t>147461</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,53%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170352</t>
+          <t>172924</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199413</t>
+          <t>202311</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>66,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,74%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>293289</t>
+          <t>296623</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>337671</t>
+          <t>341470</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>64,59%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183045</t>
+          <t>184246</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>227458</t>
+          <t>228591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44412</t>
+          <t>44110</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72130</t>
+          <t>73963</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>236806</t>
+          <t>235736</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>296457</t>
+          <t>291096</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,62%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>256533</t>
+          <t>255400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>300946</t>
+          <t>299745</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>61,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426599</t>
+          <t>424766</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>454317</t>
+          <t>454619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>686263</t>
+          <t>691624</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>745914</t>
+          <t>746984</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>76,01%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169710</t>
+          <t>169281</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203285</t>
+          <t>203367</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,73%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68842</t>
+          <t>67258</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100773</t>
+          <t>99598</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>244029</t>
+          <t>245416</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>296769</t>
+          <t>294554</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>45,49%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110772</t>
+          <t>110690</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144347</t>
+          <t>144776</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>232699</t>
+          <t>233874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>264630</t>
+          <t>266214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,78%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>350761</t>
+          <t>352976</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>403501</t>
+          <t>402114</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,17%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,1%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211563</t>
+          <t>211820</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>245862</t>
+          <t>248337</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,64%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110271</t>
+          <t>110103</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146562</t>
+          <t>144909</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,69%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>330817</t>
+          <t>334877</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>385091</t>
+          <t>384854</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>46,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>53,0%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108883</t>
+          <t>106408</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143182</t>
+          <t>142925</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224894</t>
+          <t>226547</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261185</t>
+          <t>261353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,54%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,31%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341110</t>
+          <t>341347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>395384</t>
+          <t>391324</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>47,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>53,89%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70976</t>
+          <t>71538</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98311</t>
+          <t>97940</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>36,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27205</t>
+          <t>27002</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51052</t>
+          <t>49199</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104477</t>
+          <t>104641</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>139957</t>
+          <t>142056</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,81%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>99779</t>
+          <t>100150</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127114</t>
+          <t>126552</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>64,17%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155626</t>
+          <t>157479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179473</t>
+          <t>179676</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,3%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>264810</t>
+          <t>262711</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>300290</t>
+          <t>300126</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,19%</t>
+          <t>74,15%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>174037</t>
+          <t>175367</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>203713</t>
+          <t>204432</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>91800</t>
+          <t>91782</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124154</t>
+          <t>124950</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>274997</t>
+          <t>276260</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>320302</t>
+          <t>321321</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,47%</t>
+          <t>50,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,97%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>65084</t>
+          <t>64365</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>94760</t>
+          <t>93430</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>151924</t>
+          <t>151128</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184278</t>
+          <t>184296</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,03%</t>
+          <t>54,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>224573</t>
+          <t>223554</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>269878</t>
+          <t>268615</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,53%</t>
+          <t>49,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>249551</t>
+          <t>247681</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>298074</t>
+          <t>299507</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106990</t>
+          <t>106197</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>146155</t>
+          <t>144864</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>366353</t>
+          <t>364903</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>433269</t>
+          <t>431173</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>34,81%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>306874</t>
+          <t>305441</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>355397</t>
+          <t>357267</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,75%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>487573</t>
+          <t>488864</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>526738</t>
+          <t>527531</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,12%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>805407</t>
+          <t>807503</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>872323</t>
+          <t>873773</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,54%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>443478</t>
+          <t>442313</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>494736</t>
+          <t>494858</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,93%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>189306</t>
+          <t>190344</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>237818</t>
+          <t>240019</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>641765</t>
+          <t>643290</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>717124</t>
+          <t>717220</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>244398</t>
+          <t>244276</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>295656</t>
+          <t>296821</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>542470</t>
+          <t>540269</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>590982</t>
+          <t>589944</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,74%</t>
+          <t>75,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>802297</t>
+          <t>802201</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>877656</t>
+          <t>876131</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>57,66%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1721081</t>
+          <t>1711533</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1830050</t>
+          <t>1832417</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>53,24%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>774438</t>
+          <t>776264</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>871859</t>
+          <t>875351</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2521204</t>
+          <t>2521776</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2681089</t>
+          <t>2683702</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>38,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,71%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1402553</t>
+          <t>1400186</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1511522</t>
+          <t>1521070</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2488420</t>
+          <t>2484928</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2585841</t>
+          <t>2584015</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3911793</t>
+          <t>3909180</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4071678</t>
+          <t>4071106</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,75%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2012</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2012 (tasa de respuesta: 96,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148137</t>
+          <t>148601</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>183314</t>
+          <t>181898</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>61,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79830</t>
+          <t>79626</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>114354</t>
+          <t>113102</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,39%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237080</t>
+          <t>237372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>287396</t>
+          <t>288520</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>50,01%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110475</t>
+          <t>111891</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145652</t>
+          <t>145188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>38,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>168790</t>
+          <t>170042</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203314</t>
+          <t>203518</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,61%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>289538</t>
+          <t>288414</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>339854</t>
+          <t>339562</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,19%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,86%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>251623</t>
+          <t>249165</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>296807</t>
+          <t>294617</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102410</t>
+          <t>102437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140680</t>
+          <t>142866</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>364679</t>
+          <t>361832</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>431741</t>
+          <t>425377</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>181740</t>
+          <t>183930</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226924</t>
+          <t>229382</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>365832</t>
+          <t>363646</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>404102</t>
+          <t>404075</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,7 +4562,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>553319</t>
+          <t>559683</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>620381</t>
+          <t>623228</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,27%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>157952</t>
+          <t>156893</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>194437</t>
+          <t>191424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>62,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91089</t>
+          <t>90198</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>125822</t>
+          <t>126353</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,01%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>259255</t>
+          <t>257020</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309958</t>
+          <t>307747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,79%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,42%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110143</t>
+          <t>113156</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>146628</t>
+          <t>147687</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>37,15%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>205240</t>
+          <t>204709</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239973</t>
+          <t>240864</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,99%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>325685</t>
+          <t>327896</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>376388</t>
+          <t>378623</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,57%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>149466</t>
+          <t>148223</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>187416</t>
+          <t>186973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,77%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57151</t>
+          <t>57701</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88396</t>
+          <t>88399</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,7 +5135,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>213616</t>
+          <t>214792</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>266223</t>
+          <t>267347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,87%</t>
+          <t>36,02%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170425</t>
+          <t>170868</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>208375</t>
+          <t>209618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296013</t>
+          <t>296010</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>327258</t>
+          <t>326708</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5253,7 +5253,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>476028</t>
+          <t>474904</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>528635</t>
+          <t>527459</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,13%</t>
+          <t>63,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>71,06%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>107708</t>
+          <t>106765</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136129</t>
+          <t>136572</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,03%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>34512</t>
+          <t>36244</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61192</t>
+          <t>60588</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,87%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148887</t>
+          <t>148628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>189427</t>
+          <t>190609</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>44,1%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76489</t>
+          <t>76046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>104910</t>
+          <t>105853</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,97%</t>
+          <t>35,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>49,79%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>158399</t>
+          <t>159003</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>185079</t>
+          <t>183347</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,13%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>242782</t>
+          <t>241600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>283322</t>
+          <t>283581</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>65,61%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>155391</t>
+          <t>156923</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>188296</t>
+          <t>187613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68207</t>
+          <t>67005</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>98574</t>
+          <t>97887</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,6%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>229498</t>
+          <t>231220</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>280009</t>
+          <t>278377</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,43%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,46%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>75723</t>
+          <t>76406</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>108628</t>
+          <t>107096</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>178342</t>
+          <t>179029</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208709</t>
+          <t>209911</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,4%</t>
+          <t>64,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>260926</t>
+          <t>262558</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>311437</t>
+          <t>309715</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>333272</t>
+          <t>331430</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>385851</t>
+          <t>385070</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,74%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>163755</t>
+          <t>164624</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211308</t>
+          <t>213725</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>509700</t>
+          <t>508986</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>580233</t>
+          <t>584383</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246083</t>
+          <t>246864</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>298662</t>
+          <t>300504</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>473778</t>
+          <t>471361</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>521331</t>
+          <t>520462</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>69,16%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>736786</t>
+          <t>732636</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>807319</t>
+          <t>808033</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,3%</t>
+          <t>61,35%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>371199</t>
+          <t>370140</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>426578</t>
+          <t>426544</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,76%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>156989</t>
+          <t>157750</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>206517</t>
+          <t>209241</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,64%</t>
+          <t>19,73%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>25,83%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>542688</t>
+          <t>542170</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>622570</t>
+          <t>619588</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>40,48%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>304669</t>
+          <t>304703</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>360048</t>
+          <t>361107</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>592902</t>
+          <t>590178</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>642430</t>
+          <t>641669</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>74,17%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,36%</t>
+          <t>80,27%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>908096</t>
+          <t>911078</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>987978</t>
+          <t>988496</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,52%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,55%</t>
+          <t>64,58%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1779918</t>
+          <t>1778373</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1902363</t>
+          <t>1900727</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>54,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>58,04%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>846381</t>
+          <t>846842</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>953364</t>
+          <t>949519</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,24%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2656385</t>
+          <t>2647611</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2820098</t>
+          <t>2819507</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,7%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1372213</t>
+          <t>1373849</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1494658</t>
+          <t>1496203</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>45,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2532777</t>
+          <t>2536622</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2639760</t>
+          <t>2639299</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,76%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>75,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3940618</t>
+          <t>3941209</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4104331</t>
+          <t>4113105</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,84%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2016</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2016 (tasa de respuesta: 97,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>154907</t>
+          <t>153539</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>190524</t>
+          <t>188911</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,76%</t>
+          <t>53,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>82407</t>
+          <t>81284</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113838</t>
+          <t>112584</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,5%</t>
+          <t>40,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>248703</t>
+          <t>247652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>296138</t>
+          <t>298170</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>52,38%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97626</t>
+          <t>99239</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>133243</t>
+          <t>134611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>34,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,24%</t>
+          <t>46,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>167241</t>
+          <t>168495</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198672</t>
+          <t>199795</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>70,68%</t>
+          <t>71,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>273091</t>
+          <t>271059</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>320526</t>
+          <t>321577</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,98%</t>
+          <t>47,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>56,49%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>232954</t>
+          <t>232311</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>278100</t>
+          <t>274598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>55,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75844</t>
+          <t>76169</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110781</t>
+          <t>112459</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>317433</t>
+          <t>313180</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>379421</t>
+          <t>376730</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>31,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,69%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>212357</t>
+          <t>215859</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>257503</t>
+          <t>258146</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,3%</t>
+          <t>44,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>405558</t>
+          <t>403880</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>440495</t>
+          <t>440170</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>627375</t>
+          <t>630066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>689363</t>
+          <t>693616</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>68,89%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>166696</t>
+          <t>168888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>197895</t>
+          <t>198973</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98201</t>
+          <t>98555</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>130898</t>
+          <t>132895</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>40,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>271790</t>
+          <t>273092</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321734</t>
+          <t>321298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,3%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98012</t>
+          <t>96934</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129211</t>
+          <t>127019</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>199491</t>
+          <t>197494</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>232188</t>
+          <t>231834</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,38%</t>
+          <t>59,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304562</t>
+          <t>304998</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>354506</t>
+          <t>353204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,4%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>193291</t>
+          <t>194343</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>230969</t>
+          <t>231399</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,63%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>117226</t>
+          <t>115685</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156228</t>
+          <t>155493</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,29%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>321281</t>
+          <t>320490</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>376907</t>
+          <t>374748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,72%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129468</t>
+          <t>129038</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167146</t>
+          <t>166094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,37%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222154</t>
+          <t>222889</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261156</t>
+          <t>262697</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,02%</t>
+          <t>69,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>361911</t>
+          <t>364070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>417537</t>
+          <t>418328</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,62%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>70563</t>
+          <t>72603</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>100394</t>
+          <t>101095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,72%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26861</t>
+          <t>26829</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49320</t>
+          <t>49220</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105687</t>
+          <t>105565</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142056</t>
+          <t>142033</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,33%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>107116</t>
+          <t>106415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>136947</t>
+          <t>134907</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>65,01%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169267</t>
+          <t>169367</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191726</t>
+          <t>191758</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284041</t>
+          <t>284064</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>320410</t>
+          <t>320532</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>75,23%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>166864</t>
+          <t>167306</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>196145</t>
+          <t>196653</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,75%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>75,91%</t>
+          <t>76,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>87998</t>
+          <t>85493</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117812</t>
+          <t>117688</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,45%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>43,4%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>260816</t>
+          <t>259823</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>306271</t>
+          <t>306412</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,86%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>62234</t>
+          <t>61726</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91515</t>
+          <t>91073</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,09%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153344</t>
+          <t>153468</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183158</t>
+          <t>185663</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,55%</t>
+          <t>56,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>223264</t>
+          <t>223123</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>268719</t>
+          <t>269712</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,93%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>340790</t>
+          <t>342632</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>394444</t>
+          <t>394955</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,19%</t>
+          <t>53,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>223846</t>
+          <t>223801</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>276023</t>
+          <t>275906</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>579743</t>
+          <t>580950</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>655529</t>
+          <t>653802</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>49,36%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246297</t>
+          <t>245786</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>299951</t>
+          <t>298109</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>407720</t>
+          <t>407837</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>459897</t>
+          <t>459942</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,63%</t>
+          <t>59,65%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,26%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>668956</t>
+          <t>670683</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>744742</t>
+          <t>743535</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,51%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,14%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>393760</t>
+          <t>392310</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>446059</t>
+          <t>446307</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,79%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>217355</t>
+          <t>216647</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>270353</t>
+          <t>271026</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>618109</t>
+          <t>620300</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>699833</t>
+          <t>701349</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,02%</t>
+          <t>45,12%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>299905</t>
+          <t>299657</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>352204</t>
+          <t>353654</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,21%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>538036</t>
+          <t>537363</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>591034</t>
+          <t>591742</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,56%</t>
+          <t>66,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>854521</t>
+          <t>853005</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>936245</t>
+          <t>934054</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,98%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,09%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1821769</t>
+          <t>1819409</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1933711</t>
+          <t>1934282</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,41%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1019800</t>
+          <t>1016079</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1131476</t>
+          <t>1129875</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2868467</t>
+          <t>2873027</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3039082</t>
+          <t>3037583</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,83%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1353835</t>
+          <t>1353264</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1465777</t>
+          <t>1468137</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2356588</t>
+          <t>2358189</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2468264</t>
+          <t>2471985</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,56%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3736528</t>
+          <t>3738027</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3907143</t>
+          <t>3902583</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,6%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2023</t>
+          <t>Población según si han bebido a lo largo de estas dos semanas algún tipo de bebida alcohólica en 2023 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>155510</t>
+          <t>156628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>200447</t>
+          <t>202056</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78078</t>
+          <t>78805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>104322</t>
+          <t>105927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>244645</t>
+          <t>241485</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>295263</t>
+          <t>295637</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>110996</t>
+          <t>109387</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>155933</t>
+          <t>154815</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>35,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,07%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>185313</t>
+          <t>183708</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>211557</t>
+          <t>210830</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305814</t>
+          <t>305440</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>356432</t>
+          <t>359592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,3%</t>
+          <t>59,82%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>225502</t>
+          <t>230715</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>286146</t>
+          <t>285870</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>55,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98938</t>
+          <t>100478</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>134307</t>
+          <t>138486</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>333903</t>
+          <t>341280</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>408375</t>
+          <t>410364</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,82%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230047</t>
+          <t>230323</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>290691</t>
+          <t>285478</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,57%</t>
+          <t>44,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>380078</t>
+          <t>375899</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>415447</t>
+          <t>413907</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>622203</t>
+          <t>620214</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>696675</t>
+          <t>689298</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,37%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167478</t>
+          <t>167807</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202827</t>
+          <t>202714</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75562</t>
+          <t>75668</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104240</t>
+          <t>104955</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,9%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>252465</t>
+          <t>251384</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>299942</t>
+          <t>299450</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113223</t>
+          <t>113336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148572</t>
+          <t>148243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>244428</t>
+          <t>243713</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>273106</t>
+          <t>273000</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,1%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>364776</t>
+          <t>365268</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>412253</t>
+          <t>413334</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,18%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>153232</t>
+          <t>155779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199491</t>
+          <t>199656</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>75233</t>
+          <t>78486</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158243</t>
+          <t>160776</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>219065</t>
+          <t>218925</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>353406</t>
+          <t>348665</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,23%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113066</t>
+          <t>112901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>159325</t>
+          <t>156778</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>317475</t>
+          <t>314942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>400485</t>
+          <t>397232</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,74%</t>
+          <t>66,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>434868</t>
+          <t>439609</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569209</t>
+          <t>569349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,23%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23609</t>
+          <t>23058</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41089</t>
+          <t>40705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14285</t>
+          <t>14655</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30270</t>
+          <t>30427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>50688</t>
+          <t>49889</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>137653</t>
+          <t>138037</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>155133</t>
+          <t>155684</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>87,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>194371</t>
+          <t>194001</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203433</t>
+          <t>203575</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>336710</t>
+          <t>337509</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>357128</t>
+          <t>356971</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,92%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>149548</t>
+          <t>150145</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>178127</t>
+          <t>177563</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,35%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>84145</t>
+          <t>83726</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>109222</t>
+          <t>108778</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>241261</t>
+          <t>243416</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>281916</t>
+          <t>283455</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,94%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90331</t>
+          <t>90895</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>118910</t>
+          <t>118313</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>147834</t>
+          <t>148278</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>172911</t>
+          <t>173330</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,51%</t>
+          <t>57,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>243598</t>
+          <t>242059</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>284253</t>
+          <t>282098</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,06%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>53,68%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>279374</t>
+          <t>279054</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>338475</t>
+          <t>343235</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>45,0%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>250686</t>
+          <t>248222</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>615416</t>
+          <t>624290</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>568999</t>
+          <t>572588</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>987241</t>
+          <t>995784</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,92%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>282410</t>
+          <t>277650</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>341511</t>
+          <t>341831</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>44,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>229783</t>
+          <t>220909</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>594513</t>
+          <t>596977</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>478843</t>
+          <t>470300</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>897085</t>
+          <t>893496</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>116669</t>
+          <t>126052</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>388504</t>
+          <t>391844</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85480</t>
+          <t>85630</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118547</t>
+          <t>118234</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>222597</t>
+          <t>211748</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>452552</t>
+          <t>457055</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,84%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>540216</t>
+          <t>536876</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>812051</t>
+          <t>802668</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,44%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>594484</t>
+          <t>594797</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>627551</t>
+          <t>627401</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>88,01%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1189199</t>
+          <t>1184696</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1419154</t>
+          <t>1430003</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>87,1%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1248887</t>
+          <t>1200308</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1719386</t>
+          <t>1723251</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>49,91%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>851493</t>
+          <t>850746</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1468125</t>
+          <t>1518369</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>41,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2375497</t>
+          <t>2351846</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3032422</t>
+          <t>3000156</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,43%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>42,22%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1733662</t>
+          <t>1729797</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2204161</t>
+          <t>2252740</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2184221</t>
+          <t>2133977</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2800853</t>
+          <t>2801600</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>59,8%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4072973</t>
+          <t>4105239</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4729898</t>
+          <t>4753549</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,78%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,57%</t>
+          <t>66,9%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P29A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P29A-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>121382</t>
+          <t>122970</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>153586</t>
+          <t>152897</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>45,15%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>56,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57539</t>
+          <t>58016</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>86926</t>
+          <t>88593</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>33,45%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>187223</t>
+          <t>187962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>232070</t>
+          <t>233194</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,41%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,9%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115257</t>
+          <t>115946</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147461</t>
+          <t>145873</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>42,87%</t>
+          <t>43,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>172924</t>
+          <t>171257</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>202311</t>
+          <t>201834</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>65,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>296623</t>
+          <t>295499</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>341470</t>
+          <t>340731</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>184246</t>
+          <t>184140</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>228591</t>
+          <t>227783</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44110</t>
+          <t>43652</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>73963</t>
+          <t>75145</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>235736</t>
+          <t>236748</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>291096</t>
+          <t>290925</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,6%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>255400</t>
+          <t>256208</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299745</t>
+          <t>299851</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>424766</t>
+          <t>423584</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>454619</t>
+          <t>455077</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>84,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>691624</t>
+          <t>691795</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>746984</t>
+          <t>745972</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>70,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>75,91%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>169281</t>
+          <t>168607</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>203367</t>
+          <t>203698</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,9%</t>
+          <t>53,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>67258</t>
+          <t>67461</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>99598</t>
+          <t>99494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>245416</t>
+          <t>247080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>294554</t>
+          <t>295901</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,9%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>45,7%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>110690</t>
+          <t>110359</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>144776</t>
+          <t>145450</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>233874</t>
+          <t>233978</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>266214</t>
+          <t>266011</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>352976</t>
+          <t>351629</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>402114</t>
+          <t>400450</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>54,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,1%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>211820</t>
+          <t>213310</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>248337</t>
+          <t>248564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,71%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>110103</t>
+          <t>112851</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>144909</t>
+          <t>146431</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,64%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>39,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>334877</t>
+          <t>333564</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>384854</t>
+          <t>386195</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106408</t>
+          <t>106181</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>142925</t>
+          <t>141435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>226547</t>
+          <t>225025</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261353</t>
+          <t>258605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,36%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>341347</t>
+          <t>340006</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>391324</t>
+          <t>392637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>54,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>71538</t>
+          <t>71459</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>97940</t>
+          <t>98361</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27002</t>
+          <t>26934</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49199</t>
+          <t>51149</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,8%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>104641</t>
+          <t>104831</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142056</t>
+          <t>141671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,0%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>100150</t>
+          <t>99729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>126552</t>
+          <t>126631</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157479</t>
+          <t>155529</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>179676</t>
+          <t>179744</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,2%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>262711</t>
+          <t>263096</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>300126</t>
+          <t>299936</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>74,15%</t>
+          <t>74,1%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>175367</t>
+          <t>175605</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>204432</t>
+          <t>204332</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>91782</t>
+          <t>90672</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>124950</t>
+          <t>122469</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>44,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>276260</t>
+          <t>276368</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>321321</t>
+          <t>323621</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>59,39%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>64365</t>
+          <t>64465</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>93430</t>
+          <t>93192</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>151128</t>
+          <t>153609</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>184296</t>
+          <t>185406</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>55,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>223554</t>
+          <t>221254</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>268615</t>
+          <t>268507</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,03%</t>
+          <t>40,61%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,28%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>247681</t>
+          <t>248293</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>299507</t>
+          <t>296307</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>106197</t>
+          <t>105928</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>144864</t>
+          <t>146481</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16,76%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>364903</t>
+          <t>362763</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>431173</t>
+          <t>431264</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,82%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>305441</t>
+          <t>308641</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>357267</t>
+          <t>356655</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>59,06%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>488864</t>
+          <t>487247</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>527531</t>
+          <t>527800</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>807503</t>
+          <t>807412</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>873773</t>
+          <t>875913</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,71%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>442313</t>
+          <t>441310</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>494858</t>
+          <t>491696</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>190344</t>
+          <t>188394</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>240019</t>
+          <t>239027</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>643290</t>
+          <t>639010</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>717220</t>
+          <t>719489</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>47,2%</t>
+          <t>47,35%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>244276</t>
+          <t>247438</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>296821</t>
+          <t>297824</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>540269</t>
+          <t>541261</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>589944</t>
+          <t>591894</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>802201</t>
+          <t>799932</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>876131</t>
+          <t>880411</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>52,8%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,94%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1711533</t>
+          <t>1720474</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1832417</t>
+          <t>1832180</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>53,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>776264</t>
+          <t>771836</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>875351</t>
+          <t>872284</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2521776</t>
+          <t>2512024</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2683702</t>
+          <t>2675544</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>38,1%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,71%</t>
+          <t>40,58%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1400186</t>
+          <t>1400423</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1521070</t>
+          <t>1512129</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2484928</t>
+          <t>2487995</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2584015</t>
+          <t>2588443</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>77,03%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3909180</t>
+          <t>3917338</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4071106</t>
+          <t>4080858</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>61,75%</t>
+          <t>61,9%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>148601</t>
+          <t>147017</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>181898</t>
+          <t>182480</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>79626</t>
+          <t>80818</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>113102</t>
+          <t>113960</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237372</t>
+          <t>233706</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>288520</t>
+          <t>286294</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,14%</t>
+          <t>40,51%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,01%</t>
+          <t>49,62%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>111891</t>
+          <t>111309</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145188</t>
+          <t>146772</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170042</t>
+          <t>169184</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>203518</t>
+          <t>202326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288414</t>
+          <t>290640</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>339562</t>
+          <t>343228</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,86%</t>
+          <t>59,49%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>249165</t>
+          <t>252674</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>294617</t>
+          <t>295171</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>102437</t>
+          <t>103005</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>142866</t>
+          <t>141849</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,22%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>361832</t>
+          <t>365056</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>425377</t>
+          <t>428294</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,48%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>183930</t>
+          <t>183376</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>229382</t>
+          <t>225873</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,93%</t>
+          <t>47,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>363646</t>
+          <t>364663</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>404075</t>
+          <t>403507</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>559683</t>
+          <t>556766</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>623228</t>
+          <t>620004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>62,94%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156893</t>
+          <t>157518</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>191424</t>
+          <t>193738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90198</t>
+          <t>89662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>126353</t>
+          <t>125091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,25%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>257020</t>
+          <t>257717</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>307747</t>
+          <t>308687</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,56%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113156</t>
+          <t>110842</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>147687</t>
+          <t>147062</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,15%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>204709</t>
+          <t>205971</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>240864</t>
+          <t>241400</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,75%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>327896</t>
+          <t>326956</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378623</t>
+          <t>377926</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>51,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>148223</t>
+          <t>149679</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>186973</t>
+          <t>188751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57701</t>
+          <t>57254</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88399</t>
+          <t>88374</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214792</t>
+          <t>213059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>267347</t>
+          <t>265631</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,79%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>170868</t>
+          <t>169090</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>209618</t>
+          <t>208162</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296010</t>
+          <t>296035</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>326708</t>
+          <t>327155</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>474904</t>
+          <t>476620</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>527459</t>
+          <t>529192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,3%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106765</t>
+          <t>105637</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>136572</t>
+          <t>136000</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>36244</t>
+          <t>36992</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60588</t>
+          <t>61204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>148628</t>
+          <t>149363</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>190609</t>
+          <t>189103</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,75%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>76046</t>
+          <t>76618</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>105853</t>
+          <t>106981</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>49,79%</t>
+          <t>50,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159003</t>
+          <t>158387</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>183347</t>
+          <t>182599</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,13%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,49%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>241600</t>
+          <t>243106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>283581</t>
+          <t>282846</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,44%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>156923</t>
+          <t>155471</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>187613</t>
+          <t>188862</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>67005</t>
+          <t>67333</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>97887</t>
+          <t>98246</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>231220</t>
+          <t>232427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>278377</t>
+          <t>276222</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>42,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>51,46%</t>
+          <t>51,06%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76406</t>
+          <t>75157</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>107096</t>
+          <t>108548</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>28,94%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>179029</t>
+          <t>178670</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209911</t>
+          <t>209583</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,65%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>262558</t>
+          <t>264713</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>309715</t>
+          <t>308508</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>48,54%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>57,03%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>331430</t>
+          <t>333991</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>385070</t>
+          <t>386977</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>164624</t>
+          <t>163375</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>213725</t>
+          <t>212959</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>24,03%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>508986</t>
+          <t>507581</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>584383</t>
+          <t>580956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>44,11%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>246864</t>
+          <t>244957</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>300504</t>
+          <t>297943</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>471361</t>
+          <t>472127</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>520462</t>
+          <t>521711</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>68,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>75,97%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>732636</t>
+          <t>736063</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>808033</t>
+          <t>809438</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,46%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>370140</t>
+          <t>372217</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>426544</t>
+          <t>427906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,33%</t>
+          <t>58,52%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>157750</t>
+          <t>157902</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>209241</t>
+          <t>208024</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>542170</t>
+          <t>545789</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>619588</t>
+          <t>619431</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,42%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>40,48%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>304703</t>
+          <t>303341</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>361107</t>
+          <t>359030</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>590178</t>
+          <t>591395</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>641669</t>
+          <t>641517</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>73,98%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>911078</t>
+          <t>911235</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>988496</t>
+          <t>984877</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>59,52%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,58%</t>
+          <t>64,34%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1778373</t>
+          <t>1775043</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1900727</t>
+          <t>1894175</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,84%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>846842</t>
+          <t>846100</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>949519</t>
+          <t>953775</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2647611</t>
+          <t>2645986</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2819507</t>
+          <t>2819861</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>39,16%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,71%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1373849</t>
+          <t>1380401</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1496203</t>
+          <t>1499533</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>42,16%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2536622</t>
+          <t>2532366</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2639299</t>
+          <t>2640041</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>72,76%</t>
+          <t>72,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>75,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3941209</t>
+          <t>3940855</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4113105</t>
+          <t>4114730</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>60,84%</t>
+          <t>60,86%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>153539</t>
+          <t>154302</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>188911</t>
+          <t>188083</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>53,28%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>81284</t>
+          <t>82257</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>112584</t>
+          <t>114723</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>40,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>247652</t>
+          <t>244085</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>298170</t>
+          <t>295561</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>51,92%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99239</t>
+          <t>100067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>134611</t>
+          <t>133848</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>34,44%</t>
+          <t>34,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,72%</t>
+          <t>46,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>168495</t>
+          <t>166356</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199795</t>
+          <t>198822</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,08%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>271059</t>
+          <t>273668</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>321577</t>
+          <t>325144</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>47,62%</t>
+          <t>48,08%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,12%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>232311</t>
+          <t>230452</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>274598</t>
+          <t>274058</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76169</t>
+          <t>77087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>112459</t>
+          <t>112752</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>313180</t>
+          <t>316660</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>376730</t>
+          <t>380304</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,42%</t>
+          <t>37,77%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>215859</t>
+          <t>216399</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>258146</t>
+          <t>260005</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>44,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>403880</t>
+          <t>403587</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>440170</t>
+          <t>439252</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>630066</t>
+          <t>626492</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>693616</t>
+          <t>690136</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,58%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>68,55%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>168888</t>
+          <t>165554</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>198973</t>
+          <t>198135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>57,07%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>98555</t>
+          <t>97817</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>132895</t>
+          <t>134987</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,22%</t>
+          <t>40,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>273092</t>
+          <t>274542</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>321298</t>
+          <t>323018</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,84%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>51,58%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96934</t>
+          <t>97772</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>127019</t>
+          <t>130353</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,93%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>197494</t>
+          <t>195402</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>231834</t>
+          <t>232572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,78%</t>
+          <t>59,14%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,17%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>304998</t>
+          <t>303278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>353204</t>
+          <t>351754</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,4%</t>
+          <t>56,16%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>194343</t>
+          <t>193982</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>231399</t>
+          <t>231854</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>115685</t>
+          <t>117281</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155493</t>
+          <t>155793</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,57%</t>
+          <t>31,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,09%</t>
+          <t>41,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>320490</t>
+          <t>322082</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>374748</t>
+          <t>377324</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>43,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,07%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>129038</t>
+          <t>128583</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166094</t>
+          <t>166455</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>222889</t>
+          <t>222589</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>262697</t>
+          <t>261101</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>58,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>364070</t>
+          <t>361494</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>418328</t>
+          <t>416736</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>56,41%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>72603</t>
+          <t>72139</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>101095</t>
+          <t>100449</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>34,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,72%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26829</t>
+          <t>27494</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49220</t>
+          <t>49297</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>105565</t>
+          <t>105236</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142033</t>
+          <t>140181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>32,9%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>106415</t>
+          <t>107061</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>134907</t>
+          <t>135371</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,28%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,01%</t>
+          <t>65,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169367</t>
+          <t>169290</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191758</t>
+          <t>191093</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,48%</t>
+          <t>77,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284064</t>
+          <t>285916</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>320532</t>
+          <t>320861</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,3%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>167306</t>
+          <t>166138</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>196653</t>
+          <t>195932</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>64,3%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>75,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>85493</t>
+          <t>87150</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>117688</t>
+          <t>116842</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>31,53%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>259823</t>
+          <t>262199</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>306412</t>
+          <t>306636</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,91%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>61726</t>
+          <t>62447</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>91073</t>
+          <t>92241</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>35,7%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153468</t>
+          <t>154314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>185663</t>
+          <t>184006</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>68,47%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>223123</t>
+          <t>222899</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>269712</t>
+          <t>267336</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,48%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>342632</t>
+          <t>344926</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>394955</t>
+          <t>394174</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,83%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>223801</t>
+          <t>224864</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>275906</t>
+          <t>277345</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>580950</t>
+          <t>581003</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>653802</t>
+          <t>656629</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,58%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245786</t>
+          <t>246567</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>298109</t>
+          <t>295815</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,48%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>407837</t>
+          <t>406398</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>459942</t>
+          <t>458879</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,11%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>670683</t>
+          <t>667856</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>743535</t>
+          <t>743482</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>50,64%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,14%</t>
+          <t>56,13%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>392310</t>
+          <t>390964</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>446307</t>
+          <t>445555</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>216647</t>
+          <t>216264</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>271026</t>
+          <t>270639</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>33,53%</t>
+          <t>33,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>620300</t>
+          <t>623876</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>701349</t>
+          <t>700095</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,04%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>299657</t>
+          <t>300409</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>353654</t>
+          <t>355000</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>47,41%</t>
+          <t>47,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>537363</t>
+          <t>537750</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>591742</t>
+          <t>592125</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>66,47%</t>
+          <t>66,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>853005</t>
+          <t>854259</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>934054</t>
+          <t>930478</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,88%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>60,09%</t>
+          <t>59,86%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1819409</t>
+          <t>1819001</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1934282</t>
+          <t>1933753</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>55,34%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>58,84%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1016079</t>
+          <t>1017218</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1129875</t>
+          <t>1127265</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2873027</t>
+          <t>2865621</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3037583</t>
+          <t>3032254</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,75%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1353264</t>
+          <t>1353793</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1468137</t>
+          <t>1468545</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,66%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2358189</t>
+          <t>2360799</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2471985</t>
+          <t>2470846</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,87%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3738027</t>
+          <t>3743356</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3902583</t>
+          <t>3909989</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,71%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169898</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>156628</t>
+          <t>151895</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>202056</t>
+          <t>187626</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>57,76%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>58,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>78805</t>
+          <t>85226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>105927</t>
+          <t>111371</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>26,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>241485</t>
+          <t>243869</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>295637</t>
+          <t>292093</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>45,01%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,18%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>46,01%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>131554</t>
+          <t>148947</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109387</t>
+          <t>131219</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>154815</t>
+          <t>166950</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>41,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>198952</t>
+          <t>218830</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>183708</t>
+          <t>204690</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>210830</t>
+          <t>230835</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>68,69%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>64,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>73,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>330505</t>
+          <t>367776</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>305440</t>
+          <t>342813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>359592</t>
+          <t>391037</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>54,99%</t>
+          <t>57,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,82%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>255636</t>
+          <t>259856</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>230715</t>
+          <t>229495</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>285870</t>
+          <t>287587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>43,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>100478</t>
+          <t>105301</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138486</t>
+          <t>142385</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>372606</t>
+          <t>382739</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>341280</t>
+          <t>345279</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>410364</t>
+          <t>416114</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,82%</t>
+          <t>38,73%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>260557</t>
+          <t>268533</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>230323</t>
+          <t>240802</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>285478</t>
+          <t>298894</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>55,3%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>397415</t>
+          <t>423000</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>375899</t>
+          <t>403498</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>413907</t>
+          <t>440582</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>657972</t>
+          <t>691533</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>620214</t>
+          <t>658158</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>689298</t>
+          <t>728993</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,18%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>67,86%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>516193</t>
+          <t>528389</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>516193</t>
+          <t>528389</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>516193</t>
+          <t>528389</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514385</t>
+          <t>545883</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514385</t>
+          <t>545883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514385</t>
+          <t>545883</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1030578</t>
+          <t>1074272</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1030578</t>
+          <t>1074272</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1030578</t>
+          <t>1074272</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187312</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>167807</t>
+          <t>171303</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>202714</t>
+          <t>204239</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>59,28%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89812</t>
+          <t>88779</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75668</t>
+          <t>73651</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104955</t>
+          <t>102452</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>24,94%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>20,69%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>28,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>274998</t>
+          <t>276092</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>251384</t>
+          <t>253931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>299450</t>
+          <t>298964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,49%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>130864</t>
+          <t>128681</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>113336</t>
+          <t>111754</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>148243</t>
+          <t>144690</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>258856</t>
+          <t>267171</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>243713</t>
+          <t>253498</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>273000</t>
+          <t>282299</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>71,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,3%</t>
+          <t>79,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>389720</t>
+          <t>395852</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>365268</t>
+          <t>372980</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>413334</t>
+          <t>418013</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>62,21%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348668</t>
+          <t>355950</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348668</t>
+          <t>355950</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348668</t>
+          <t>355950</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664718</t>
+          <t>671944</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664718</t>
+          <t>671944</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664718</t>
+          <t>671944</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>178179</t>
+          <t>203436</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>155779</t>
+          <t>178207</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>199656</t>
+          <t>227896</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>49,84%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>124346</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>78486</t>
+          <t>120686</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>160776</t>
+          <t>157660</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>28,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,8%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>302524</t>
+          <t>341803</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>218925</t>
+          <t>308576</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>348665</t>
+          <t>374845</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>42,99%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>38,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>44,23%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>134378</t>
+          <t>169709</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>112901</t>
+          <t>145249</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>156778</t>
+          <t>194938</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>351372</t>
+          <t>283595</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>314942</t>
+          <t>264301</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>397232</t>
+          <t>301275</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>67,21%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,2%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>71,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>485750</t>
+          <t>453304</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>439609</t>
+          <t>420262</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>569349</t>
+          <t>486531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>57,01%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>52,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>61,19%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>312557</t>
+          <t>373145</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>788274</t>
+          <t>795107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23058</t>
+          <t>26100</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40705</t>
+          <t>45515</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14655</t>
+          <t>17580</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30427</t>
+          <t>35433</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49889</t>
+          <t>58055</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>13,41%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>147596</t>
+          <t>171528</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>138037</t>
+          <t>160150</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>155684</t>
+          <t>179565</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>200073</t>
+          <t>216370</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>194001</t>
+          <t>209635</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>203575</t>
+          <t>220917</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,98%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>347669</t>
+          <t>387897</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>337509</t>
+          <t>374824</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>356971</t>
+          <t>397446</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>86,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>91,81%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208656</t>
+          <t>227215</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>387398</t>
+          <t>432879</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>164637</t>
+          <t>162549</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>150145</t>
+          <t>147803</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>177563</t>
+          <t>175679</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>55,93%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>83726</t>
+          <t>85150</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>108778</t>
+          <t>111469</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>37,23%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>42,32%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>261057</t>
+          <t>260743</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>243416</t>
+          <t>243491</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>283455</t>
+          <t>282206</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>48,89%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>46,32%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,94%</t>
+          <t>52,92%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>103821</t>
+          <t>106980</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90895</t>
+          <t>93850</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>118313</t>
+          <t>121726</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>160636</t>
+          <t>165556</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>148278</t>
+          <t>152281</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>173330</t>
+          <t>178600</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>62,49%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,68%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,43%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>264457</t>
+          <t>272537</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>242059</t>
+          <t>251074</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>282098</t>
+          <t>289789</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>50,32%</t>
+          <t>51,11%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,06%</t>
+          <t>47,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>268458</t>
+          <t>269529</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>268458</t>
+          <t>269529</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>268458</t>
+          <t>269529</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>525514</t>
+          <t>533280</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525514</t>
+          <t>533280</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>525514</t>
+          <t>533280</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>308093</t>
+          <t>350886</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>279054</t>
+          <t>317608</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>343235</t>
+          <t>380139</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,94%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>401553</t>
+          <t>236397</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>248222</t>
+          <t>212566</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>624290</t>
+          <t>261072</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>47,51%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>73,86%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>709646</t>
+          <t>587283</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>572588</t>
+          <t>548999</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>995784</t>
+          <t>625933</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>39,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>67,92%</t>
+          <t>42,23%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>312792</t>
+          <t>364260</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>277650</t>
+          <t>335007</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>341831</t>
+          <t>397538</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>50,38%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>443646</t>
+          <t>530532</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>220909</t>
+          <t>505857</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>596977</t>
+          <t>554363</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>69,18%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>26,14%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>72,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>756438</t>
+          <t>894792</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>470300</t>
+          <t>856142</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>893496</t>
+          <t>933076</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>51,6%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>62,96%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>620885</t>
+          <t>715146</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>620885</t>
+          <t>715146</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>620885</t>
+          <t>715146</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>845199</t>
+          <t>766929</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>845199</t>
+          <t>766929</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>845199</t>
+          <t>766929</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1466084</t>
+          <t>1482075</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1466084</t>
+          <t>1482075</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1466084</t>
+          <t>1482075</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>277537</t>
+          <t>314336</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>126052</t>
+          <t>283955</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>391844</t>
+          <t>342689</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>85630</t>
+          <t>97577</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>118234</t>
+          <t>136834</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>377362</t>
+          <t>429289</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>211748</t>
+          <t>395615</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>457055</t>
+          <t>469126</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>28,85%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>651183</t>
+          <t>483736</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>536876</t>
+          <t>455383</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>802668</t>
+          <t>514117</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>70,12%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>64,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>613206</t>
+          <t>713050</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>594797</t>
+          <t>691170</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>627401</t>
+          <t>730427</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1264389</t>
+          <t>1196787</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1184696</t>
+          <t>1156950</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1430003</t>
+          <t>1230461</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>75,67%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>713031</t>
+          <t>828004</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>713031</t>
+          <t>828004</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>713031</t>
+          <t>828004</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1641751</t>
+          <t>1626076</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1641751</t>
+          <t>1626076</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1641751</t>
+          <t>1626076</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1580302</t>
+          <t>1682411</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1200308</t>
+          <t>1614562</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1723251</t>
+          <t>1751951</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>45,77%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,91%</t>
+          <t>49,7%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1028192</t>
+          <t>907649</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>850746</t>
+          <t>859504</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1518369</t>
+          <t>958057</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>24,36%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>41,57%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>2608494</t>
+          <t>2590061</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2351846</t>
+          <t>2494475</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3000156</t>
+          <t>2670491</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>36,71%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>34,4%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1872746</t>
+          <t>1842374</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1729797</t>
+          <t>1772834</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2252740</t>
+          <t>1910223</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>54,23%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>50,3%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2624154</t>
+          <t>2818105</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2133977</t>
+          <t>2767697</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2801600</t>
+          <t>2866250</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>58,43%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>76,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>4496901</t>
+          <t>4660478</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4105239</t>
+          <t>4580048</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4753549</t>
+          <t>4756064</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>64,28%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>65,6%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3453048</t>
+          <t>3524785</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3453048</t>
+          <t>3524785</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3453048</t>
+          <t>3524785</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3652346</t>
+          <t>3725754</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3652346</t>
+          <t>3725754</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3652346</t>
+          <t>3725754</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7105395</t>
+          <t>7250539</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7105395</t>
+          <t>7250539</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7105395</t>
+          <t>7250539</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
